--- a/result_gsea/LUSC_FAT1_chip/LUSC_MSigDB_Hallmark_2020/LUSC_GSEA_MSigDB_Hallmark_2020_results.xlsx
+++ b/result_gsea/LUSC_FAT1_chip/LUSC_MSigDB_Hallmark_2020/LUSC_GSEA_MSigDB_Hallmark_2020_results.xlsx
@@ -492,19 +492,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7352112561539601</v>
+        <v>0.73521125615396</v>
       </c>
       <c r="D2" t="n">
-        <v>2.389410576574853</v>
+        <v>2.502129409183744</v>
       </c>
       <c r="E2" t="n">
         <v>0.001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008075635217648217</v>
+        <v>0.00164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TGF-beta Signaling</t>
+          <t>Hypoxia</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7123467133187481</v>
+        <v>0.6133211765545691</v>
       </c>
       <c r="D3" t="n">
-        <v>2.362943745024363</v>
+        <v>2.483150455257662</v>
       </c>
       <c r="E3" t="n">
         <v>0.001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00484538113058893</v>
+        <v>0.001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31/54</t>
+          <t>94/199</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13.11%</t>
+          <t>14.47%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PMEPA1;BMP2;LTBP2;SMAD7;NCOR2;SKI;SERPINE1;BMPR2;HIPK2;KLF10;ACVR1;SMAD6;TGFB1;SMAD3;SMAD1;SPTBN1;BCAR3;THBS1;RAB31;NOG;ID1;PPP1R15A;TJP1;XIAP;APC;SMURF1;ENG;TGFBR1;FURIN;MAP3K7;ARID4B</t>
+          <t>EGFR;KLF7;COL5A1;CHST3;TMEM45A;TGFBI;TGFB3;PRKCA;P4HA2;CAV1;CA12;GPC1;EXT1;NDRG1;CAVIN3;SERPINE1;AKAP12;PGF;NDST1;STC1;ADORA2B;TPBG;NOCT;GPC4;ETS1;SLC2A1;SRPX;LOX;MYH9;PDGFB;PKP1;DDIT4;DCN;MAP3K1;FOSL2;PFKFB3;TNFAIP3;PPARGC1A;VLDLR;CCNG2;CCN1;BGN;ANGPTL4;ERRFI1;ALDOA;ADM;LARGE1;PDK3;GYS1;CAVIN1;HS3ST1;ACKR3;FOXO3;BHLHE40;P4HA1;CCN2;AMPD3;TPST2;SLC2A3;PPP1R15A;HDLBP;PAM;TGM2;PLAUR;EDN2;IER3;KDELR3;PGM2;IDS;VEGFA;F3;JUN;B3GALT6;FOS;ZNF292;SDC2;PHKG1;KLF6;HAS1;GBE1;PFKP;ERO1A;ATP7A;CP;PKLR;CDKN1A;NFIL3;TES;CITED2;ENO2;PGM1;PPP1R3C;SDC4;CSRP2</t>
         </is>
       </c>
     </row>
@@ -572,37 +572,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hypoxia</t>
+          <t>Angiogenesis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.613321176554569</v>
+        <v>0.7965767596813714</v>
       </c>
       <c r="D4" t="n">
-        <v>2.358989085694386</v>
+        <v>2.417957566460121</v>
       </c>
       <c r="E4" t="n">
         <v>0.001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003230254087059287</v>
+        <v>0.002186666666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>94/199</t>
+          <t>23/36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14.47%</t>
+          <t>10.70%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>EGFR;KLF7;COL5A1;CHST3;TMEM45A;TGFBI;TGFB3;PRKCA;P4HA2;CAV1;CA12;GPC1;EXT1;NDRG1;CAVIN3;SERPINE1;AKAP12;PGF;NDST1;STC1;ADORA2B;TPBG;NOCT;GPC4;ETS1;SLC2A1;SRPX;LOX;MYH9;PDGFB;PKP1;DDIT4;DCN;MAP3K1;FOSL2;PFKFB3;TNFAIP3;PPARGC1A;VLDLR;CCNG2;CCN1;BGN;ANGPTL4;ERRFI1;ALDOA;ADM;LARGE1;PDK3;GYS1;CAVIN1;HS3ST1;ACKR3;FOXO3;BHLHE40;P4HA1;CCN2;AMPD3;TPST2;SLC2A3;PPP1R15A;HDLBP;PAM;TGM2;PLAUR;EDN2;IER3;KDELR3;PGM2;IDS;VEGFA;F3;JUN;B3GALT6;FOS;ZNF292;SDC2;PHKG1;KLF6;HAS1;GBE1;PFKP;ERO1A;ATP7A;CP;PKLR;CDKN1A;NFIL3;TES;CITED2;ENO2;PGM1;PPP1R3C;SDC4;CSRP2</t>
+          <t>PDGFA;COL5A2;VAV2;JAG2;NRP1;VCAN;JAG1;POSTN;FSTL1;STC1;COL3A1;ITGAV;CXCL6;SLCO2A1;THBD;TNFRSF21;LRPAP1;APP;CCND2;PTK2;VEGFA;LUM;KCNJ8</t>
         </is>
       </c>
     </row>
@@ -614,37 +614,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apical Junction</t>
+          <t>TGF-beta Signaling</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6267465712337194</v>
+        <v>0.7123467133187473</v>
       </c>
       <c r="D5" t="n">
-        <v>2.32203505547322</v>
+        <v>2.411855150334593</v>
       </c>
       <c r="E5" t="n">
         <v>0.001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003634035847941698</v>
+        <v>0.00164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>96/197</t>
+          <t>31/54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15.61%</t>
+          <t>13.11%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IRS1;LAMA3;LAMC2;EGFR;COL16A1;CDH3;COL17A1;LAMB3;GNAI1;ITGA3;BMP1;TGFBI;VAV2;ITGB4;CDH8;ITGA2;CDH11;FBN1;MMP2;NECTIN1;ACTN1;VCAN;DSC3;CDH6;LIMA1;CERCAM;THY1;PARVA;AMIGO2;VCL;SHROOM2;PKD1;NEXN;ITGB1;SIRPA;MYH10;LDLRAP1;PARD6G;FSCN1;ACTG2;ICAM1;ADAM9;MYH9;NLGN2;FYB1;CDH4;CX3CL1;SPEG;CLDN14;MYL9;ADAMTS5;SHC1;VWF;CD276;PLCG1;MSN;MAPK11;ZYX;RRAS;NFASC;NECTIN3;ICAM5;CNN2;CTNND1;PTEN;FLNC;MAP3K20;MMP9;RASA1;PIK3CB;VCAM1;SRC;RAC2;ACTN4;PTK2;TJP1;CD209;JAM3;CD34;NF2;KRT31;RSU1;TSPAN4;MPZL1;MPZL2;TRO;NF1;NEGR1;CLDN19;TSC1;CD99;DLG1;THBS3;EXOC4;EPB41L2;NRXN2</t>
+          <t>PMEPA1;BMP2;LTBP2;SMAD7;NCOR2;SKI;SERPINE1;BMPR2;HIPK2;KLF10;ACVR1;SMAD6;TGFB1;SMAD3;SMAD1;SPTBN1;BCAR3;THBS1;RAB31;NOG;ID1;PPP1R15A;TJP1;XIAP;APC;SMURF1;ENG;TGFBR1;FURIN;MAP3K7;ARID4B</t>
         </is>
       </c>
     </row>
@@ -656,37 +656,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Angiogenesis</t>
+          <t>Apical Junction</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7965767596813709</v>
+        <v>0.6267465712337195</v>
       </c>
       <c r="D6" t="n">
-        <v>2.30485343251484</v>
+        <v>2.403050615061176</v>
       </c>
       <c r="E6" t="n">
         <v>0.001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002907228678353358</v>
+        <v>0.001312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23/36</t>
+          <t>96/197</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10.70%</t>
+          <t>15.61%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PDGFA;COL5A2;VAV2;JAG2;NRP1;VCAN;JAG1;POSTN;FSTL1;STC1;COL3A1;ITGAV;CXCL6;SLCO2A1;THBD;TNFRSF21;LRPAP1;APP;CCND2;PTK2;VEGFA;LUM;KCNJ8</t>
+          <t>IRS1;LAMA3;LAMC2;EGFR;COL16A1;CDH3;COL17A1;LAMB3;GNAI1;ITGA3;BMP1;TGFBI;VAV2;ITGB4;CDH8;ITGA2;CDH11;FBN1;MMP2;NECTIN1;ACTN1;VCAN;DSC3;CDH6;LIMA1;CERCAM;THY1;PARVA;AMIGO2;VCL;SHROOM2;PKD1;NEXN;ITGB1;SIRPA;MYH10;LDLRAP1;PARD6G;FSCN1;ACTG2;ICAM1;ADAM9;MYH9;NLGN2;FYB1;CDH4;CX3CL1;SPEG;CLDN14;MYL9;ADAMTS5;SHC1;VWF;CD276;PLCG1;MSN;MAPK11;ZYX;RRAS;NFASC;NECTIN3;ICAM5;CNN2;CTNND1;PTEN;FLNC;MAP3K20;MMP9;RASA1;PIK3CB;VCAM1;SRC;RAC2;ACTN4;PTK2;TJP1;CD209;JAM3;CD34;NF2;KRT31;RSU1;TSPAN4;MPZL1;MPZL2;TRO;NF1;NEGR1;CLDN19;TSC1;CD99;DLG1;THBS3;EXOC4;EPB41L2;NRXN2</t>
         </is>
       </c>
     </row>
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5411720488674404</v>
+        <v>0.5411720488674422</v>
       </c>
       <c r="D7" t="n">
-        <v>2.197411435603803</v>
+        <v>2.286439133475534</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00392156862745098</v>
+        <v>0.001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008614010898824765</v>
+        <v>0.004920000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6432953977832876</v>
+        <v>0.6432953977832886</v>
       </c>
       <c r="D8" t="n">
-        <v>2.174392116317288</v>
+        <v>2.266230238297509</v>
       </c>
       <c r="E8" t="n">
         <v>0.001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008767832522018064</v>
+        <v>0.00492</v>
       </c>
       <c r="G8" t="n">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7903194686475562</v>
+        <v>0.7903194686475554</v>
       </c>
       <c r="D9" t="n">
-        <v>2.138683507388452</v>
+        <v>2.226006430761967</v>
       </c>
       <c r="E9" t="n">
         <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0113058893047075</v>
+        <v>0.006149999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5261382872053383</v>
+        <v>0.5261382872053391</v>
       </c>
       <c r="D10" t="n">
-        <v>2.134874257370655</v>
+        <v>2.220669699649611</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001976284584980237</v>
+        <v>0.00199203187250996</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01040859650274659</v>
+        <v>0.005831111111111112</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -866,37 +866,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coagulation</t>
+          <t>Estrogen Response Early</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6073952808819894</v>
+        <v>0.5502373579876825</v>
       </c>
       <c r="D11" t="n">
-        <v>2.124405260561404</v>
+        <v>2.189275871108234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001945525291828794</v>
+        <v>0.001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01114437660035454</v>
+        <v>0.007052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.048</v>
+        <v>0.027</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53/138</t>
+          <t>73/198</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.24%</t>
+          <t>11.05%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KLF7;CFH;LRP1;BMP1;PLAT;MMP10;ITGA2;FBN1;TIMP3;FN1;PLAU;MMP2;DUSP6;C9;COMP;MMP1;MMP3;SERPINE1;RAPGEF3;CFI;HTRA1;MMP14;ITGB3;PROC;ADAM9;CPQ;C1R;PDGFB;THBD;MMP7;PRSS23;CRIP2;CTSO;C1S;VWF;P2RY1;CTSK;MMP11;THBS1;SPARC;MMP9;GNG12;C3;SERPING1;CAPN2;FYN;F3;TFPI2;WDR1;CFB;PREP;CTSB;FURIN</t>
+          <t>FHL2;FOXC1;THSD4;CELSR2;MED13L;CELSR1;IGF1R;SLC24A3;P2RY2;PTGES;CCND1;KAZN;SEC14L2;CA12;NRIP1;NCOR2;GJA1;MAST4;MYOF;AFF1;ADCY9;NAV2;FLNB;ENDOD1;SVIL;TPBG;MPPED2;SLC2A1;SLC16A1;PAPSS2;HR;SYT12;KLF10;RPS6KA2;PRSS23;HSPB8;OLFML3;INPP5F;TIAM1;CYP26B1;CD44;LAD1;GFRA1;OPN3;IGFBP4;SEMA3B;DLC1;PGR;RAB31;CISH;TSKU;AQP3;KRT15;EGR3;BHLHE40;AREG;KDM4B;BCL11B;KRT13;PODXL;RARA;TGM2;FRK;SH3BP5;SLC1A4;ABAT;RETREG1;NBL1;CBFA2T3;TFAP2C;FOS;ZNF185;SLC7A2</t>
         </is>
       </c>
     </row>
@@ -908,37 +908,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estrogen Response Early</t>
+          <t>Estrogen Response Late</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5502373579876825</v>
+        <v>0.5126453747086201</v>
       </c>
       <c r="D12" t="n">
-        <v>2.114395962705692</v>
+        <v>2.178580065728101</v>
       </c>
       <c r="E12" t="n">
         <v>0.001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01115905957347754</v>
+        <v>0.007007272727272727</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>73/198</t>
+          <t>60/197</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>10.71%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FHL2;FOXC1;THSD4;CELSR2;MED13L;CELSR1;IGF1R;SLC24A3;P2RY2;PTGES;CCND1;KAZN;SEC14L2;CA12;NRIP1;NCOR2;GJA1;MAST4;MYOF;AFF1;ADCY9;NAV2;FLNB;ENDOD1;SVIL;TPBG;MPPED2;SLC2A1;SLC16A1;PAPSS2;HR;SYT12;KLF10;RPS6KA2;PRSS23;HSPB8;OLFML3;INPP5F;TIAM1;CYP26B1;CD44;LAD1;GFRA1;OPN3;IGFBP4;SEMA3B;DLC1;PGR;RAB31;CISH;TSKU;AQP3;KRT15;EGR3;BHLHE40;AREG;KDM4B;BCL11B;KRT13;PODXL;RARA;TGM2;FRK;SH3BP5;SLC1A4;ABAT;RETREG1;NBL1;CBFA2T3;TFAP2C;FOS;ZNF185;SLC7A2</t>
+          <t>LAMC2;FOXC1;DLG5;CELSR2;CPE;SLC24A3;PTGES;CCND1;CAV1;CA12;NRIP1;NCOR2;TRIM29;MYOF;AFF1;GJB3;FLNB;ATP2B4;CA2;TPBG;FGFR3;SLC16A1;PTGER3;PAPSS2;HR;HOMER2;RPS6KA2;PRSS23;HSPB8;GPER1;ST6GALNAC2;TIAM1;CYP26B1;PKP3;SERPINA3;FABP5;CD44;JAK1;OPN3;IGFBP4;SEMA3B;PLK4;PLXNB1;LARGE1;PGR;RAB31;CISH;EGR3;SCUBE2;HSPA4L;AREG;PRLR;KRT13;FRK;SLC1A4;TFPI2;NBL1;TPSAB1;TFAP2C;FOS</t>
         </is>
       </c>
     </row>
@@ -950,37 +950,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estrogen Response Late</t>
+          <t>Coagulation</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5126453747086204</v>
+        <v>0.6073952808819889</v>
       </c>
       <c r="D13" t="n">
-        <v>2.106865038797605</v>
+        <v>2.17372404706973</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001915708812260536</v>
+        <v>0.002008032128514056</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01117129538441337</v>
+        <v>0.006560000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.052</v>
+        <v>0.031</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60/197</t>
+          <t>53/138</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.71%</t>
+          <t>12.24%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>LAMC2;FOXC1;DLG5;CELSR2;CPE;SLC24A3;PTGES;CCND1;CAV1;CA12;NRIP1;NCOR2;TRIM29;MYOF;AFF1;GJB3;FLNB;ATP2B4;CA2;TPBG;FGFR3;SLC16A1;PTGER3;PAPSS2;HR;HOMER2;RPS6KA2;PRSS23;HSPB8;GPER1;ST6GALNAC2;TIAM1;CYP26B1;PKP3;SERPINA3;FABP5;CD44;JAK1;OPN3;IGFBP4;SEMA3B;PLK4;PLXNB1;LARGE1;PGR;RAB31;CISH;EGR3;SCUBE2;HSPA4L;AREG;PRLR;KRT13;FRK;SLC1A4;TFPI2;NBL1;TPSAB1;TFAP2C;FOS</t>
+          <t>KLF7;CFH;LRP1;BMP1;PLAT;MMP10;ITGA2;FBN1;TIMP3;FN1;PLAU;MMP2;DUSP6;C9;COMP;MMP1;MMP3;SERPINE1;RAPGEF3;CFI;HTRA1;MMP14;ITGB3;PROC;ADAM9;CPQ;C1R;PDGFB;THBD;MMP7;PRSS23;CRIP2;CTSO;C1S;VWF;P2RY1;CTSK;MMP11;THBS1;SPARC;MMP9;GNG12;C3;SERPING1;CAPN2;FYN;F3;TFPI2;WDR1;CFB;PREP;CTSB;FURIN</t>
         </is>
       </c>
     </row>
@@ -992,37 +992,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hedgehog Signaling</t>
+          <t>Wnt-beta Catenin Signaling</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7119019495962434</v>
+        <v>0.653600702917434</v>
       </c>
       <c r="D14" t="n">
-        <v>2.057344361618934</v>
+        <v>2.168812886395549</v>
       </c>
       <c r="E14" t="n">
         <v>0.001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01652399206072635</v>
+        <v>0.006307692307692308</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21/36</t>
+          <t>21/42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12.76%</t>
+          <t>12.67%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CELSR1;CDK6;NRP2;NRP1;UNC5C;THY1;ADGRG1;ETS2;MYH9;PML;VLDLR;HEY2;RASA1;L1CAM;NKX6-1;VEGFA;TLE3;DPYSL2;PTCH1;GLI1;NF1</t>
+          <t>GNAI1;FZD1;NOTCH1;JAG2;NCOR2;JAG1;WNT5B;WNT6;FZD8;NOTCH4;HEY2;PPARD;DLL1;NKD1;CCND2;HDAC11;CSNK1E;PTCH1;MAML1;LEF1;ADAM17</t>
         </is>
       </c>
     </row>
@@ -1034,37 +1034,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wnt-beta Catenin Signaling</t>
+          <t>Androgen Response</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6536007029174337</v>
+        <v>0.5342515675535573</v>
       </c>
       <c r="D15" t="n">
-        <v>2.056283548556302</v>
+        <v>2.167503545715732</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001</v>
+        <v>0.001988071570576541</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01545907313092659</v>
+        <v>0.006091428571428571</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21/42</t>
+          <t>39/100</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12.67%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GNAI1;FZD1;NOTCH1;JAG2;NCOR2;JAG1;WNT5B;WNT6;FZD8;NOTCH4;HEY2;PPARD;DLL1;NKD1;CCND2;HDAC11;CSNK1E;PTCH1;MAML1;LEF1;ADAM17</t>
+          <t>PMEPA1;ANKH;PTPN21;CDK6;CCND1;ACTN1;MAF;NDRG1;AKAP12;NKX3-1;INPP4B;ITGAV;BMPR1B;ALDH1A3;PTK2B;ZMIZ1;HOMER2;SEC24D;PDLIM5;HMGCS1;IQGAP2;SELENOP;GUCY1A1;ARID5B;ELK4;ADAMTS1;SLC38A2;LIFR;AKT1;LMAN1;ACSL3;ELL2;PLPP1;PIAS1;SRF;CAMKK2;HERC3;B4GALT1;RRP12</t>
         </is>
       </c>
     </row>
@@ -1076,37 +1076,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Androgen Response</t>
+          <t>TNF-alpha Signaling via NF-kB</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5342515675535571</v>
+        <v>0.6337480601088076</v>
       </c>
       <c r="D16" t="n">
-        <v>2.037959776658594</v>
+        <v>2.102382186990061</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01195219123505976</v>
+        <v>0.01606425702811245</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01679732125270829</v>
+        <v>0.01038666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.077</v>
+        <v>0.053</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39/100</t>
+          <t>96/198</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>14.63%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PMEPA1;ANKH;PTPN21;CDK6;CCND1;ACTN1;MAF;NDRG1;AKAP12;NKX3-1;INPP4B;ITGAV;BMPR1B;ALDH1A3;PTK2B;ZMIZ1;HOMER2;SEC24D;PDLIM5;HMGCS1;IQGAP2;SELENOP;GUCY1A1;ARID5B;ELK4;ADAMTS1;SLC38A2;LIFR;AKT1;LMAN1;ACSL3;ELL2;PLPP1;PIAS1;SRF;CAMKK2;HERC3;B4GALT1;RRP12</t>
+          <t>PMEPA1;TNC;LAMB3;BMP2;CCND1;REL;FJX1;PHLDA1;NFAT5;PLAU;INHBA;PTGS2;NFKB1;PLK2;JAG1;PTX3;SERPINE1;PANX1;CSF1;ZC3H12A;TNFAIP6;ICAM1;ETS2;CXCL6;ABCA1;KLF10;GFPT2;FOSL2;CXCL1;TLR2;GEM;PFKFB3;PDLIM5;TNFAIP3;FOSL1;RNF19B;TNF;LIF;SMAD3;PTGER4;CD44;TRIB1;LDLR;CCN1;RELB;PTPRE;IL1A;DENND5A;EHD1;TNFAIP2;ACKR3;EGR3;KDM6B;BHLHE40;PER1;SLC2A3;PPP1R15A;IER5;AREG;NFKB2;CXCL3;CFLAR;PLAUR;IER3;MXD1;EGR1;SPHK1;VEGFA;F3;IL7R;PLPP3;IFIT2;KLF9;FUT4;IL1B;SNN;JUN;SIK1;FOS;PHLDA2;SPSB1;KLF6;CSF2;CEBPB;DUSP5;G0S2;CCL20;CDKN1A;NFIL3;IL6ST;TRIP10;SERPINB8;IFIH1;TNIP2;SDC4;RELA</t>
         </is>
       </c>
     </row>
@@ -1118,37 +1118,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mitotic Spindle</t>
+          <t>Hedgehog Signaling</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6228160475583844</v>
+        <v>0.7119019495962448</v>
       </c>
       <c r="D17" t="n">
-        <v>2.037429405332818</v>
+        <v>2.078427377441651</v>
       </c>
       <c r="E17" t="n">
-        <v>0.005802707930367505</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01574748867441402</v>
+        <v>0.0115825</v>
       </c>
       <c r="G17" t="n">
-        <v>0.077</v>
+        <v>0.057</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>108/198</t>
+          <t>21/36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19.62%</t>
+          <t>12.76%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SYNPO;PXN;TRIO;ARHGAP5;DST;FLNA;CLIP2;FLNB;BCR;ARHGAP10;AKAP13;ITSN1;VCL;SHROOM2;ARHGEF12;MYH10;PLEKHG2;FGD6;FSCN1;NOTCH2;DYNC1H1;CDC42EP4;RICTOR;MYO1E;HOOK3;NCK2;PALLD;MYH9;CEP72;SUN2;TIAM1;MARK4;RAPGEF5;CLIP1;PDLIM5;NUMA1;ALMS1;CLASP1;RASAL2;PKD2;CCDC88A;SPTBN1;ABR;CDC42BPA;ABL1;CENPE;MID1;ROCK1;WASF2;NIN;CTTN;INCENP;SPTAN1;RASA1;BCAR1;ALS2;ANLN;LLGL1;ARAP3;MAP3K11;CENPF;RFC1;ACTN4;NET1;APC;KIF20B;MYO9B;SORBS2;LATS1;BIN1;KIFAP3;KIF1B;KIF3B;CEP250;NEDD9;PCNT;NF1;TUBGCP6;RABGAP1;CNTROB;KLC1;FGD4;PAFAH1B1;CKAP5;BCL2L11;ARFGEF1;TSC1;DOCK4;PCM1;DLG1;SOS1;RALBP1;STK38L;EPB41L2;CAPZB;TUBGCP5;RAB3GAP1;SEPTIN9;SMC1A;CNTRL;SHROOM1;CEP192;TAOK2;ARHGEF11;SMC3;SMC4;HDAC6;CDC42EP1</t>
+          <t>CELSR1;CDK6;NRP2;NRP1;UNC5C;THY1;ADGRG1;ETS2;MYH9;PML;VLDLR;HEY2;RASA1;L1CAM;NKX6-1;VEGFA;TLE3;DPYSL2;PTCH1;GLI1;NF1</t>
         </is>
       </c>
     </row>
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6358718068639453</v>
+        <v>0.6358718068639448</v>
       </c>
       <c r="D18" t="n">
-        <v>1.997042617808117</v>
+        <v>2.077417421364368</v>
       </c>
       <c r="E18" t="n">
         <v>0.001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02175671135107579</v>
+        <v>0.01090117647058824</v>
       </c>
       <c r="G18" t="n">
-        <v>0.092</v>
+        <v>0.057</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1202,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TNF-alpha Signaling via NF-kB</t>
+          <t>KRAS Signaling Up</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6337480601088091</v>
+        <v>0.5811079544455364</v>
       </c>
       <c r="D19" t="n">
-        <v>1.964714345757304</v>
+        <v>2.050550057684847</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01814516129032258</v>
+        <v>0.003891050583657588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0278160768607883</v>
+        <v>0.01430444444444444</v>
       </c>
       <c r="G19" t="n">
-        <v>0.107</v>
+        <v>0.076</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>96/198</t>
+          <t>79/200</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14.63%</t>
+          <t>12.67%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PMEPA1;TNC;LAMB3;BMP2;CCND1;REL;FJX1;PHLDA1;NFAT5;PLAU;INHBA;PTGS2;NFKB1;PLK2;JAG1;PTX3;SERPINE1;PANX1;CSF1;ZC3H12A;TNFAIP6;ICAM1;ETS2;CXCL6;ABCA1;KLF10;GFPT2;FOSL2;CXCL1;TLR2;GEM;PFKFB3;PDLIM5;TNFAIP3;FOSL1;RNF19B;TNF;LIF;SMAD3;PTGER4;CD44;TRIB1;LDLR;CCN1;RELB;PTPRE;IL1A;DENND5A;EHD1;TNFAIP2;ACKR3;EGR3;KDM6B;BHLHE40;PER1;SLC2A3;PPP1R15A;IER5;AREG;NFKB2;CXCL3;CFLAR;PLAUR;IER3;MXD1;EGR1;SPHK1;VEGFA;F3;IL7R;PLPP3;IFIT2;KLF9;FUT4;IL1B;SNN;JUN;SIK1;FOS;PHLDA2;SPSB1;KLF6;CSF2;CEBPB;DUSP5;G0S2;CCL20;CDKN1A;NFIL3;IL6ST;TRIP10;SERPINB8;IFIH1;TNIP2;SDC4;RELA</t>
+          <t>ANKH;CFH;ANO1;CPE;PLAT;BMP2;MMP10;ITGA2;EPHB2;PLAU;INHBA;PLEK2;PTGS2;NRP1;DUSP6;CROT;SPON1;AKAP12;PRRX1;CA2;IL1RL2;SOX9;ETS1;ADGRA2;ALDH1A3;WNT7A;SCN1B;DCBLD2;GFPT2;MAP3K1;TRIB2;TNFAIP3;GPNMB;LIF;ITGBL1;SERPINA3;TRIB1;HOXD11;MYCN;ANGPTL4;CBL;SNAP25;SEMA3B;SATB1;MMP11;NIN;GUCY1A1;BTBD3;PTPRR;MMP9;MAFB;ADAM8;PPP1R15A;CCND2;PRDM1;F13A1;MALL;PLAUR;APOD;IL7R;IL1B;PPBP;EREG;KCNN4;CCSER2;CFB;ENG;MTMR10;CSF2;G0S2;ERO1A;CCL20;FLT4;ST6GAL1;GALNT3;MMD;MPZL2;STRN;ADAM17</t>
         </is>
       </c>
     </row>
@@ -1244,37 +1244,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oxidative Phosphorylation</t>
+          <t>Mitotic Spindle</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.5089137417615424</v>
+        <v>0.6228160475583848</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.945229814680746</v>
+        <v>2.029867836546994</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.003944773175542407</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1305301645338209</v>
+        <v>0.0164</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1393939393939394</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>111/200</t>
+          <t>108/198</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22.22%</t>
+          <t>19.62%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CYB5A;UQCR11;NDUFA2;MRPL34;ATP5MG;ACADSB;ECI1;COX11;UQCRQ;ATP5PO;SLC25A20;TIMM8B;NDUFB5;NDUFB1;ACAT1;NDUFB8;NDUFA9;ATP5MC1;COX5A;COX6A1;NDUFS7;NDUFB6;NDUFB7;NDUFB2;ATP5PF;NDUFA7;ATP5PD;COX5B;NDUFA4;ATP5MF;MPC1;MRPS12;COX7B;NDUFAB1;SUCLG1;TIMM50;MRPL11;ATP6V1F;ISCA1;SDHD;COX17;MTRF1;MRPS15;NDUFS3;COX7A2;SURF1;COX7C;COX6B1;COX4I1;ATP6V0B;POLR2F;TIMM10;ATP5MC3;TIMM9;NDUFB4;ACAA2;NDUFC2;ATP5F1D;TIMM13;RHOT1;UQCRB;UQCR10;NDUFS4;COX6C;MRPL35;FH;FXN;NDUFA3;ETFA;IDH1;ECH1;MDH1;CYC1;NDUFS8;MGST3;UQCRFS1;CYCS;FDX1;ETFB;ATP5F1C;PDHB;NDUFA1;SDHB;SLC25A4;NDUFA5;COX7A2L;HSD17B10;NDUFA8;MRPS22;UQCRC2;ATP5MC2;DECR1;MRPL15;ALAS1;VDAC3;HTRA2;NDUFA6;HCCS;ATP5F1E;PHB2;AIFM1;ATP5ME;ISCU;ECHS1;UQCRH;PRDX3;PHYH;SLC25A5;BCKDHA;TOMM22;PMPCA</t>
+          <t>SYNPO;PXN;TRIO;ARHGAP5;DST;FLNA;CLIP2;FLNB;BCR;ARHGAP10;AKAP13;ITSN1;VCL;SHROOM2;ARHGEF12;MYH10;PLEKHG2;FGD6;FSCN1;NOTCH2;DYNC1H1;CDC42EP4;RICTOR;MYO1E;HOOK3;NCK2;PALLD;MYH9;CEP72;SUN2;TIAM1;MARK4;RAPGEF5;CLIP1;PDLIM5;NUMA1;ALMS1;CLASP1;RASAL2;PKD2;CCDC88A;SPTBN1;ABR;CDC42BPA;ABL1;CENPE;MID1;ROCK1;WASF2;NIN;CTTN;INCENP;SPTAN1;RASA1;BCAR1;ALS2;ANLN;LLGL1;ARAP3;MAP3K11;CENPF;RFC1;ACTN4;NET1;APC;KIF20B;MYO9B;SORBS2;LATS1;BIN1;KIFAP3;KIF1B;KIF3B;CEP250;NEDD9;PCNT;NF1;TUBGCP6;RABGAP1;CNTROB;KLC1;FGD4;PAFAH1B1;CKAP5;BCL2L11;ARFGEF1;TSC1;DOCK4;PCM1;DLG1;SOS1;RALBP1;STK38L;EPB41L2;CAPZB;TUBGCP5;RAB3GAP1;SEPTIN9;SMC1A;CNTRL;SHROOM1;CEP192;TAOK2;ARHGEF11;SMC3;SMC4;HDAC6;CDC42EP1</t>
         </is>
       </c>
     </row>
@@ -1286,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KRAS Signaling Up</t>
+          <t>Oxidative Phosphorylation</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5811079544455361</v>
+        <v>-0.5089137417615441</v>
       </c>
       <c r="D21" t="n">
-        <v>1.938119303729681</v>
+        <v>-1.972712223977249</v>
       </c>
       <c r="E21" t="n">
-        <v>0.005847953216374269</v>
+        <v>0.03985507246376811</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03213252749758975</v>
+        <v>0.10872</v>
       </c>
       <c r="G21" t="n">
-        <v>0.126</v>
+        <v>0.1227364185110664</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>79/200</t>
+          <t>111/200</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12.67%</t>
+          <t>22.22%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ANKH;CFH;ANO1;CPE;PLAT;BMP2;MMP10;ITGA2;EPHB2;PLAU;INHBA;PLEK2;PTGS2;NRP1;DUSP6;CROT;SPON1;AKAP12;PRRX1;CA2;IL1RL2;SOX9;ETS1;ADGRA2;ALDH1A3;WNT7A;SCN1B;DCBLD2;GFPT2;MAP3K1;TRIB2;TNFAIP3;GPNMB;LIF;ITGBL1;SERPINA3;TRIB1;HOXD11;MYCN;ANGPTL4;CBL;SNAP25;SEMA3B;SATB1;MMP11;NIN;GUCY1A1;BTBD3;PTPRR;MMP9;MAFB;ADAM8;PPP1R15A;CCND2;PRDM1;F13A1;MALL;PLAUR;APOD;IL7R;IL1B;PPBP;EREG;KCNN4;CCSER2;CFB;ENG;MTMR10;CSF2;G0S2;ERO1A;CCL20;FLT4;ST6GAL1;GALNT3;MMD;MPZL2;STRN;ADAM17</t>
+          <t>CYB5A;UQCR11;NDUFA2;MRPL34;ATP5MG;ACADSB;ECI1;COX11;UQCRQ;ATP5PO;SLC25A20;TIMM8B;NDUFB5;NDUFB1;ACAT1;NDUFB8;NDUFA9;ATP5MC1;COX5A;COX6A1;NDUFS7;NDUFB6;NDUFB7;NDUFB2;ATP5PF;NDUFA7;ATP5PD;COX5B;NDUFA4;ATP5MF;MPC1;MRPS12;COX7B;NDUFAB1;SUCLG1;TIMM50;MRPL11;ATP6V1F;ISCA1;SDHD;COX17;MTRF1;MRPS15;NDUFS3;COX7A2;SURF1;COX7C;COX6B1;COX4I1;ATP6V0B;POLR2F;TIMM10;ATP5MC3;TIMM9;NDUFB4;ACAA2;NDUFC2;ATP5F1D;TIMM13;RHOT1;UQCRB;UQCR10;NDUFS4;COX6C;MRPL35;FH;FXN;NDUFA3;ETFA;IDH1;ECH1;MDH1;CYC1;NDUFS8;MGST3;UQCRFS1;CYCS;FDX1;ETFB;ATP5F1C;PDHB;NDUFA1;SDHB;SLC25A4;NDUFA5;COX7A2L;HSD17B10;NDUFA8;MRPS22;UQCRC2;ATP5MC2;DECR1;MRPL15;ALAS1;VDAC3;HTRA2;NDUFA6;HCCS;ATP5F1E;PHB2;AIFM1;ATP5ME;ISCU;ECHS1;UQCRH;PRDX3;PHYH;SLC25A5;BCKDHA;TOMM22;PMPCA</t>
         </is>
       </c>
     </row>
@@ -1332,19 +1332,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.512831159879556</v>
+        <v>0.5128311598795565</v>
       </c>
       <c r="D22" t="n">
-        <v>1.936656915152231</v>
+        <v>1.95250482464266</v>
       </c>
       <c r="E22" t="n">
-        <v>0.007751937984496124</v>
+        <v>0.003868471953578337</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03068741382706323</v>
+        <v>0.02706</v>
       </c>
       <c r="G22" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1374,19 +1374,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4305099150988091</v>
+        <v>0.4305099150988089</v>
       </c>
       <c r="D23" t="n">
-        <v>1.919826662927862</v>
+        <v>1.945289660184942</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02504816955684008</v>
+        <v>0.01768172888015717</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03276400574017276</v>
+        <v>0.02694285714285714</v>
       </c>
       <c r="G23" t="n">
-        <v>0.141</v>
+        <v>0.133</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4488711253713437</v>
+        <v>0.4488711253713424</v>
       </c>
       <c r="D24" t="n">
-        <v>1.872687295534199</v>
+        <v>1.897130633238222</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02099236641221374</v>
+        <v>0.01844262295081967</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04037817608824109</v>
+        <v>0.03570727272727273</v>
       </c>
       <c r="G24" t="n">
         <v>0.162</v>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.503190451961528</v>
+        <v>0.5031904519615283</v>
       </c>
       <c r="D25" t="n">
-        <v>1.760449559537201</v>
+        <v>1.895614223278085</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03536345776031434</v>
+        <v>0.02330097087378641</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07310205444845039</v>
+        <v>0.03451130434782608</v>
       </c>
       <c r="G25" t="n">
-        <v>0.252</v>
+        <v>0.163</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5017609240098599</v>
+        <v>0.5017609240098601</v>
       </c>
       <c r="D26" t="n">
-        <v>1.728665057143187</v>
+        <v>1.832522333411321</v>
       </c>
       <c r="E26" t="n">
-        <v>0.049800796812749</v>
+        <v>0.03427419354838709</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08250607314030596</v>
+        <v>0.05043</v>
       </c>
       <c r="G26" t="n">
-        <v>0.269</v>
+        <v>0.207</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1538,37 +1538,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Protein Secretion</t>
+          <t>Inflammatory Response</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4521207706524726</v>
+        <v>0.5718845569783094</v>
       </c>
       <c r="D27" t="n">
-        <v>1.696975939989938</v>
+        <v>1.815006214263922</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07768924302788845</v>
+        <v>0.05905511811023622</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09167461099074256</v>
+        <v>0.053464</v>
       </c>
       <c r="G27" t="n">
-        <v>0.301</v>
+        <v>0.221</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>36/96</t>
+          <t>81/199</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22.11%</t>
+          <t>13.70%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>EGFR;SSPN;DST;IGF2R;ABCA1;CAV2;DOP1A;SEC24D;ATP1A1;SEC31A;GBF1;CLCN3;PAM;ADAM10;GALC;RAB22A;ARFGEF2;GOLGA4;KIF1B;LMAN1;MON2;ATP7A;SCRN1;MAPK1;ARFGEF1;YKT6;LAMP2;CLN5;NAPA;VAMP3;M6PR;TMED10;ARCN1;STAM;USO1;AP1G1</t>
+          <t>PCDH7;OSMR;PDPN;HRH1;HAS2;P2RY2;ITGA5;IL4R;INHBA;AXL;NFKB1;CD82;SERPINE1;IL1R1;ADORA2B;TPBG;MMP14;BDKRB1;TLR3;CSF1;SGMS2;ITGB3;SLC7A1;RNF144B;TNFAIP6;ICAM1;ITGB8;CXCL6;ABCA1;SCN1B;PTAFR;MET;DCBLD2;TLR2;IRAK2;LIF;CX3CL1;IFITM1;PTGER4;PVR;GNA15;LDLR;PTPRE;CLEC5A;IL1A;ADM;NOD2;IL18R1;MEFV;TNFSF10;ACVR1B;ROS1;STAB1;SLC4A4;BST2;PLAUR;TAPBP;MXD1;SPHK1;F3;IL7R;ATP2A2;IL1B;EMP3;EREG;ACVR2A;IL15;LY6E;KLF6;KIF1B;SLC7A2;CCL20;PTGIR;CDKN1A;LAMP3;TNFSF15;ATP2C1;NLRP3;BEST1;P2RX7;RAF1</t>
         </is>
       </c>
     </row>
@@ -1580,37 +1580,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inflammatory Response</t>
+          <t>Protein Secretion</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.571884556978309</v>
+        <v>0.4521207706524724</v>
       </c>
       <c r="D28" t="n">
-        <v>1.674311298094334</v>
+        <v>1.76028266353907</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06275303643724696</v>
+        <v>0.08155339805825243</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09945455371888305</v>
+        <v>0.06881692307692307</v>
       </c>
       <c r="G28" t="n">
-        <v>0.319</v>
+        <v>0.258</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>81/199</t>
+          <t>36/96</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>22.11%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PCDH7;OSMR;PDPN;HRH1;HAS2;P2RY2;ITGA5;IL4R;INHBA;AXL;NFKB1;CD82;SERPINE1;IL1R1;ADORA2B;TPBG;MMP14;BDKRB1;TLR3;CSF1;SGMS2;ITGB3;SLC7A1;RNF144B;TNFAIP6;ICAM1;ITGB8;CXCL6;ABCA1;SCN1B;PTAFR;MET;DCBLD2;TLR2;IRAK2;LIF;CX3CL1;IFITM1;PTGER4;PVR;GNA15;LDLR;PTPRE;CLEC5A;IL1A;ADM;NOD2;IL18R1;MEFV;TNFSF10;ACVR1B;ROS1;STAB1;SLC4A4;BST2;PLAUR;TAPBP;MXD1;SPHK1;F3;IL7R;ATP2A2;IL1B;EMP3;EREG;ACVR2A;IL15;LY6E;KLF6;KIF1B;SLC7A2;CCL20;PTGIR;CDKN1A;LAMP3;TNFSF15;ATP2C1;NLRP3;BEST1;P2RX7;RAF1</t>
+          <t>EGFR;SSPN;DST;IGF2R;ABCA1;CAV2;DOP1A;SEC24D;ATP1A1;SEC31A;GBF1;CLCN3;PAM;ADAM10;GALC;RAB22A;ARFGEF2;GOLGA4;KIF1B;LMAN1;MON2;ATP7A;SCRN1;MAPK1;ARFGEF1;YKT6;LAMP2;CLN5;NAPA;VAMP3;M6PR;TMED10;ARCN1;STAM;USO1;AP1G1</t>
         </is>
       </c>
     </row>
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3613538539402119</v>
+        <v>0.3613538539402113</v>
       </c>
       <c r="D29" t="n">
-        <v>1.651858820234602</v>
+        <v>1.684589301095704</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03653846153846154</v>
+        <v>0.05708661417322835</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1059403701515185</v>
+        <v>0.09408740740740741</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338</v>
+        <v>0.321</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1664,37 +1664,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cholesterol Homeostasis</t>
+          <t>IL-6/JAK/STAT3 Signaling</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.4246039694247831</v>
+        <v>0.5369900508162491</v>
       </c>
       <c r="D30" t="n">
-        <v>1.603745365962817</v>
+        <v>1.666294084658845</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07707509881422925</v>
+        <v>0.08686868686868687</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1251723458735474</v>
+        <v>0.09845857142857141</v>
       </c>
       <c r="G30" t="n">
-        <v>0.387</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22/74</t>
+          <t>34/87</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>14.22%</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>GNAI1;ANTXR2;JAG1;TNFRSF12A;GPX8;CPEB2;CYP51A1;HMGCS1;FABP5;LDLR;ERRFI1;SEMA3B;PDK3;NIBAN1;ABCA2;PLAUR;NFIL3;ANXA5;ATXN2;FASN;SQLE;SREBF2</t>
+          <t>OSMR;PDGFC;IL4R;TNFRSF12A;IL1R1;CSF1;ITGB3;IL17RA;CXCL1;TLR2;TNF;ITGA4;TNFRSF21;TGFB1;CD44;CBL;IL1R2;FAS;IL18R1;ACVR1B;CXCL3;LTBR;TNFRSF1A;IL1B;JUN;STAT3;IL7;CSF2;STAT2;PTPN11;IL6ST;ACVRL1;A2M;IFNGR1</t>
         </is>
       </c>
     </row>
@@ -1706,37 +1706,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IL-6/JAK/STAT3 Signaling</t>
+          <t>Cholesterol Homeostasis</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5369900508162471</v>
+        <v>0.4246039694247823</v>
       </c>
       <c r="D31" t="n">
-        <v>1.563695629252401</v>
+        <v>1.624914240599531</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1124497991967871</v>
+        <v>0.09465020576131687</v>
       </c>
       <c r="F31" t="n">
-        <v>0.14229826193856</v>
+        <v>0.1131034482758621</v>
       </c>
       <c r="G31" t="n">
-        <v>0.431</v>
+        <v>0.372</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>34/87</t>
+          <t>22/74</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14.22%</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OSMR;PDGFC;IL4R;TNFRSF12A;IL1R1;CSF1;ITGB3;IL17RA;CXCL1;TLR2;TNF;ITGA4;TNFRSF21;TGFB1;CD44;CBL;IL1R2;FAS;IL18R1;ACVR1B;CXCL3;LTBR;TNFRSF1A;IL1B;JUN;STAT3;IL7;CSF2;STAT2;PTPN11;IL6ST;ACVRL1;A2M;IFNGR1</t>
+          <t>GNAI1;ANTXR2;JAG1;TNFRSF12A;GPX8;CPEB2;CYP51A1;HMGCS1;FABP5;LDLR;ERRFI1;SEMA3B;PDK3;NIBAN1;ABCA2;PLAUR;NFIL3;ANXA5;ATXN2;FASN;SQLE;SREBF2</t>
         </is>
       </c>
     </row>
@@ -1752,19 +1752,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.3589006306758282</v>
+        <v>0.3589006306758278</v>
       </c>
       <c r="D32" t="n">
-        <v>1.471508461335421</v>
+        <v>1.464854816095312</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04572564612326044</v>
+        <v>0.032719836400818</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1915002297944981</v>
+        <v>0.1871786666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>0.511</v>
+        <v>0.52</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1794,19 +1794,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3082909526101817</v>
+        <v>0.3082909526101821</v>
       </c>
       <c r="D33" t="n">
-        <v>1.378365476250515</v>
+        <v>1.426751290502676</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2080152671755725</v>
+        <v>0.1765913757700205</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2422690565294465</v>
+        <v>0.2047354838709677</v>
       </c>
       <c r="G33" t="n">
-        <v>0.597</v>
+        <v>0.552</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1832,37 +1832,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reactive Oxygen Species Pathway</t>
+          <t>Interferon Alpha Response</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.3676347976736987</v>
+        <v>0.487532321641612</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.301521511702217</v>
+        <v>1.301858460296574</v>
       </c>
       <c r="E34" t="n">
-        <v>0.227364185110664</v>
+        <v>0.2830957230142566</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.28664125</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6535353535353535</v>
+        <v>0.663</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18/48</t>
+          <t>39/97</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15.44%</t>
+          <t>20.64%</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>HHEX;TXNRD1;NQO1;GSR;GCLC;GCLM;SRXN1;GLRX;PRDX2;SOD1;GLRX2;NDUFB4;PRDX1;LAMTOR5;TXN;ATOX1;MGST1;FTL</t>
+          <t>TENT5A;IL4R;HELZ2;CSF1;TRIM5;DDX60;IFITM1;C1S;SAMD9;CASP1;UBA7;LPAR6;MOV10;BST2;HERC6;EPSTI1;IFIT2;CD47;IL15;LY6E;IFI44;IL7;IFITM3;LAMP3;STAT2;IFITM2;IFIH1;TMEM140;SP110;SAMD9L;OASL;TRIM14;IRF2;IFIT3;IFI44L;RSAD2;EIF2AK2;NCOA7;DHX58</t>
         </is>
       </c>
     </row>
@@ -1874,37 +1874,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Interferon Alpha Response</t>
+          <t>Reactive Oxygen Species Pathway</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4875323216416115</v>
+        <v>-0.3676347976736955</v>
       </c>
       <c r="D35" t="n">
-        <v>1.297808383538387</v>
+        <v>-1.293984314966661</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2767676767676768</v>
+        <v>0.2471042471042471</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2955682489659248</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.665</v>
+        <v>0.6800804828973843</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>39/97</t>
+          <t>18/48</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20.64%</t>
+          <t>15.44%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>TENT5A;IL4R;HELZ2;CSF1;TRIM5;DDX60;IFITM1;C1S;SAMD9;CASP1;UBA7;LPAR6;MOV10;BST2;HERC6;EPSTI1;IFIT2;CD47;IL15;LY6E;IFI44;IL7;IFITM3;LAMP3;STAT2;IFITM2;IFIH1;TMEM140;SP110;SAMD9L;OASL;TRIM14;IRF2;IFIT3;IFI44L;RSAD2;EIF2AK2;NCOA7;DHX58</t>
+          <t>HHEX;TXNRD1;NQO1;GSR;GCLC;GCLM;SRXN1;GLRX;PRDX2;SOD1;GLRX2;NDUFB4;PRDX1;LAMTOR5;TXN;ATOX1;MGST1;FTL</t>
         </is>
       </c>
     </row>
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.3001697912643896</v>
+        <v>0.3001697912643922</v>
       </c>
       <c r="D36" t="n">
-        <v>1.249260806842947</v>
+        <v>1.241045340777898</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2682445759368836</v>
+        <v>0.2880658436213992</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3222912600497788</v>
+        <v>0.3271551515151515</v>
       </c>
       <c r="G36" t="n">
-        <v>0.699</v>
+        <v>0.713</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1962,19 +1962,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4196229609195248</v>
+        <v>0.4196229609195255</v>
       </c>
       <c r="D37" t="n">
-        <v>1.206669808089736</v>
+        <v>1.194990263963034</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3407258064516129</v>
+        <v>0.3270440251572327</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3473948255685965</v>
+        <v>0.3537576470588236</v>
       </c>
       <c r="G37" t="n">
-        <v>0.734</v>
+        <v>0.752</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2004,19 +2004,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.2631293882766907</v>
+        <v>-0.2631293882766909</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.179125281122965</v>
+        <v>-1.189354402078372</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2797494780793319</v>
+        <v>0.2722222222222222</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9101767215112736</v>
+        <v>0.89916</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7464646464646465</v>
+        <v>0.7686116700201208</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.2666826518191567</v>
+        <v>0.2666826518191562</v>
       </c>
       <c r="D39" t="n">
-        <v>1.152494197923575</v>
+        <v>1.173441843817194</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3036437246963563</v>
+        <v>0.2655601659751037</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3823697909339036</v>
+        <v>0.3615497142857143</v>
       </c>
       <c r="G39" t="n">
-        <v>0.765</v>
+        <v>0.773</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2084,37 +2084,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pperoxisome</t>
+          <t>Allograft Rejection</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.2381117580458607</v>
+        <v>0.3740835703318389</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.067390832015218</v>
+        <v>1.091443555285835</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3885480572597137</v>
+        <v>0.4068825910931174</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8751371115173675</v>
+        <v>0.41943</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8323232323232324</v>
+        <v>0.826</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>28/103</t>
+          <t>45/200</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17.51%</t>
+          <t>12.72%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SLC27A2;ALDH1A1;SLC25A19;ABCC8;ECI2;SULT2B1;CACNA1B;NR1I2;MSH2;HSD3B7;ABCD2;ISOC1;DIO1;HSD11B2;SOD1;PRDX1;TTR;HSD17B11;IDH1;PEX11A;ECH1;ACOT8;PEX2;SLC25A4;IDI1;FDPS;ABCC5;FIS1</t>
+          <t>EGFR;IL11;IL4R;INHBA;DYRK3;FLNA;THY1;TGFB2;ETS1;TLR3;CSF1;ICAM1;GCNT1;EIF4G3;F2R;FYB1;TLR2;ELF4;TNF;TGFB1;LIF;IFNAR2;FAS;RPL3L;MMP9;CCL11;STAB1;CCND2;BCAT1;IKBKB;TLR6;TAPBP;CD47;AKT1;EIF3A;IL1B;EREG;ACVR2A;IL15;GALNT1;IL7;KRT1;MAP3K7;IL27RA;NLRP3</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.2605827205008263</v>
+        <v>0.2605827205008265</v>
       </c>
       <c r="D41" t="n">
-        <v>1.066921896196688</v>
+        <v>1.06275524081916</v>
       </c>
       <c r="E41" t="n">
-        <v>0.376278118609407</v>
+        <v>0.3443983402489627</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4494988291423194</v>
+        <v>0.4357081081081081</v>
       </c>
       <c r="G41" t="n">
-        <v>0.819</v>
+        <v>0.843</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2168,37 +2168,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Allograft Rejection</t>
+          <t>Pperoxisome</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.3740835703318382</v>
+        <v>-0.2381117580458633</v>
       </c>
       <c r="D42" t="n">
-        <v>1.050989518508253</v>
+        <v>-1.056985175165452</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4387351778656127</v>
+        <v>0.3977272727272727</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4524974846818455</v>
+        <v>0.90081</v>
       </c>
       <c r="G42" t="n">
-        <v>0.829</v>
+        <v>0.8440643863179075</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45/200</t>
+          <t>28/103</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12.72%</t>
+          <t>17.51%</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>EGFR;IL11;IL4R;INHBA;DYRK3;FLNA;THY1;TGFB2;ETS1;TLR3;CSF1;ICAM1;GCNT1;EIF4G3;F2R;FYB1;TLR2;ELF4;TNF;TGFB1;LIF;IFNAR2;FAS;RPL3L;MMP9;CCL11;STAB1;CCND2;BCAT1;IKBKB;TLR6;TAPBP;CD47;AKT1;EIF3A;IL1B;EREG;ACVR2A;IL15;GALNT1;IL7;KRT1;MAP3K7;IL27RA;NLRP3</t>
+          <t>SLC27A2;ALDH1A1;SLC25A19;ABCC8;ECI2;SULT2B1;CACNA1B;NR1I2;MSH2;HSD3B7;ABCD2;ISOC1;DIO1;HSD11B2;SOD1;PRDX1;TTR;HSD17B11;IDH1;PEX11A;ECH1;ACOT8;PEX2;SLC25A4;IDI1;FDPS;ABCC5;FIS1</t>
         </is>
       </c>
     </row>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.2244324785970182</v>
+        <v>0.2244324785970204</v>
       </c>
       <c r="D43" t="n">
-        <v>1.025428461397939</v>
+        <v>1.042159834229324</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4365384615384615</v>
+        <v>0.3760162601626016</v>
       </c>
       <c r="F43" t="n">
-        <v>0.46366897152276</v>
+        <v>0.4428431578947368</v>
       </c>
       <c r="G43" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2256,19 +2256,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.2268316186744699</v>
+        <v>0.2268316186744707</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8901329719252948</v>
+        <v>0.9080779195192231</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5526838966202783</v>
+        <v>0.5021097046413502</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5791265788902188</v>
+        <v>0.5582307692307693</v>
       </c>
       <c r="G44" t="n">
-        <v>0.903</v>
+        <v>0.915</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2298,19 +2298,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2906636004369971</v>
+        <v>0.2906636004369977</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8708224030979548</v>
+        <v>0.9021087714305998</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5690721649484536</v>
+        <v>0.5325443786982249</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5817283829032893</v>
+        <v>0.5498919999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.911</v>
+        <v>0.916</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2336,37 +2336,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>E2F Targets</t>
+          <t>DNA Repair</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.2864792835229529</v>
+        <v>-0.210605849866559</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.8568895369602353</v>
+        <v>-0.8543588641474466</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.5627450980392157</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>76/200</t>
+          <t>50/148</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23.08%</t>
+          <t>21.85%</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>RNASEH2A;MTHFD2;EZH2;NME1;SHMT1;DCTPP1;ASF1A;RAD51C;HMMR;UBE2T;DONSON;MXD3;EXOSC8;SPC24;NAA38;SPC25;MSH2;RPA3;PSIP1;CKS2;CDKN3;CCNE1;TIPIN;DCK;PPM1D;POLA2;DDX39A;ORC6;PRIM2;STMN1;RAD51AP1;POLE4;ASF1B;ING3;CENPM;DSCC1;SUV39H1;CHEK2;BIRC5;PTTG1;DUT;CKS1B;RRM2;TMPO;POP7;RBBP7;CDC25A;RFC2;KIF22;EED;SRSF2;GINS1;CDK1;CDKN2A;SNRPB;UBE2S;SPAG5;PHF5A;KPNA2;RFC3;AURKB;UNG;DEPDC1;TBRG4;MELK;HMGA1;LUC7L3;H2AX;PCNA;CDKN1B;JPT1;HMGB3;GINS3;RPA2;H2AZ1;MCM6</t>
+          <t>POLR2I;MPC2;PDE6G;NME1;RFC4;PRIM1;CCNO;RPA3;POLR2H;COX17;POLA2;VPS37D;POLR1C;NT5C;TARBP2;SURF1;ADA;POLE4;MPG;GTF2A2;POLR2F;SUPT4H1;SNAPC5;POLR3GL;DUT;TAF9;NME4;POLR2J;SAC3D1;NME3;ALYREF;RFC2;GTF2B;APRT;ARL6IP1;NELFCD;DGUOK;GTF2H5;POLR3C;GTF3C5;RBX1;HPRT1;RFC3;POLL;RAD51;ZWINT;RFC5;POLR2K;POLR2D;PCNA</t>
         </is>
       </c>
     </row>
@@ -2378,37 +2378,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DNA Repair</t>
+          <t>Myc Targets V1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.2106058498665579</v>
+        <v>-0.2497111776680913</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.8526312219055789</v>
+        <v>-0.8228232516564553</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5516528925619835</v>
+        <v>0.5792452830188679</v>
       </c>
       <c r="F47" t="n">
-        <v>0.875624619134674</v>
+        <v>0.92364</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9363636363636364</v>
+        <v>0.9446680080482898</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50/148</t>
+          <t>83/199</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21.85%</t>
+          <t>28.86%</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>POLR2I;MPC2;PDE6G;NME1;RFC4;PRIM1;CCNO;RPA3;POLR2H;COX17;POLA2;VPS37D;POLR1C;NT5C;TARBP2;SURF1;ADA;POLE4;MPG;GTF2A2;POLR2F;SUPT4H1;SNAPC5;POLR3GL;DUT;TAF9;NME4;POLR2J;SAC3D1;NME3;ALYREF;RFC2;GTF2B;APRT;ARL6IP1;NELFCD;DGUOK;GTF2H5;POLR3C;GTF3C5;RBX1;HPRT1;RFC3;POLL;RAD51;ZWINT;RFC5;POLR2K;POLR2D;PCNA</t>
+          <t>IFRD1;NME1;SNRPG;RFC4;COX5A;ODC1;RPS10;LSM7;LSM2;HSPE1;NDUFAB1;HDDC2;PSMB3;SSBP1;NHP2;C1QBP;EIF1AX;GLO1;DUT;PSMC6;NOP16;ACP1;SNRPD1;TXNL4A;UBA2;RPS6;SNRPD2;CYC1;SRSF7;PSMD14;SRSF2;ERH;RPL14;RPS5;ILF2;MRPL9;PSMA4;VDAC3;PSMD8;HPRT1;KPNA2;SRSF3;RRP9;GNL3;EXOSC7;PSMA1;PHB2;TUFM;FBL;EEF1B2;PRDX3;PCNA;CCT4;CCT2;SNRPB2;SNRPA;H2AZ1;POLE3;MCM6;VBP1;PSMC4;RPS3;MRPS18B;NPM1;RPL18;MRPL23;PSMA7;CCT3;PA2G4;RPLP0;RAN;RACK1;CDK4;SRPK1;UBE2E1;TRA2B;PSMD3;PTGES3;CCT7;MAD2L1;RPS2;TFDP1;RANBP1</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Myc Targets V1</t>
+          <t>E2F Targets</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.2497111776680921</v>
+        <v>-0.2864792835229524</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.8186920936364661</v>
+        <v>-0.8165366611710029</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5763052208835341</v>
+        <v>0.6174089068825911</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7957691303212326</v>
+        <v>0.8002285714285714</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9464646464646465</v>
+        <v>0.9466800804828974</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>83/199</t>
+          <t>76/200</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28.86%</t>
+          <t>23.08%</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>IFRD1;NME1;SNRPG;RFC4;COX5A;ODC1;RPS10;LSM7;LSM2;HSPE1;NDUFAB1;HDDC2;PSMB3;SSBP1;NHP2;C1QBP;EIF1AX;GLO1;DUT;PSMC6;NOP16;ACP1;SNRPD1;TXNL4A;UBA2;RPS6;SNRPD2;CYC1;SRSF7;PSMD14;SRSF2;ERH;RPL14;RPS5;ILF2;MRPL9;PSMA4;VDAC3;PSMD8;HPRT1;KPNA2;SRSF3;RRP9;GNL3;EXOSC7;PSMA1;PHB2;TUFM;FBL;EEF1B2;PRDX3;PCNA;CCT4;CCT2;SNRPB2;SNRPA;H2AZ1;POLE3;MCM6;VBP1;PSMC4;RPS3;MRPS18B;NPM1;RPL18;MRPL23;PSMA7;CCT3;PA2G4;RPLP0;RAN;RACK1;CDK4;SRPK1;UBE2E1;TRA2B;PSMD3;PTGES3;CCT7;MAD2L1;RPS2;TFDP1;RANBP1</t>
+          <t>RNASEH2A;MTHFD2;EZH2;NME1;SHMT1;DCTPP1;ASF1A;RAD51C;HMMR;UBE2T;DONSON;MXD3;EXOSC8;SPC24;NAA38;SPC25;MSH2;RPA3;PSIP1;CKS2;CDKN3;CCNE1;TIPIN;DCK;PPM1D;POLA2;DDX39A;ORC6;PRIM2;STMN1;RAD51AP1;POLE4;ASF1B;ING3;CENPM;DSCC1;SUV39H1;CHEK2;BIRC5;PTTG1;DUT;CKS1B;RRM2;TMPO;POP7;RBBP7;CDC25A;RFC2;KIF22;EED;SRSF2;GINS1;CDK1;CDKN2A;SNRPB;UBE2S;SPAG5;PHF5A;KPNA2;RFC3;AURKB;UNG;DEPDC1;TBRG4;MELK;HMGA1;LUC7L3;H2AX;PCNA;CDKN1B;JPT1;HMGB3;GINS3;RPA2;H2AZ1;MCM6</t>
         </is>
       </c>
     </row>
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.1891785144456712</v>
+        <v>-0.1891785144456704</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7756412661966634</v>
+        <v>-0.7525295258689054</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7850098619329389</v>
+        <v>0.7762096774193549</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7470749542961609</v>
+        <v>0.7742250000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9585858585858585</v>
+        <v>0.96579476861167</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2508,19 +2508,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.23747057616999</v>
+        <v>0.2374705761699901</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7442981778080943</v>
+        <v>0.7389872401572897</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7709611451942741</v>
+        <v>0.797244094488189</v>
       </c>
       <c r="F50" t="n">
-        <v>0.69391372857987</v>
+        <v>0.70592</v>
       </c>
       <c r="G50" t="n">
-        <v>0.958</v>
+        <v>0.957</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.1925912856255362</v>
+        <v>-0.192591285625539</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.590034410065199</v>
+        <v>-0.5770204920119947</v>
       </c>
       <c r="E51" t="n">
-        <v>0.781563126252505</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8537070891732683</v>
+        <v>0.8628400000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9838383838383838</v>
+        <v>0.9909456740442656</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
